--- a/results_scenario_1/tables/table_fmf_scenario_1.xlsx
+++ b/results_scenario_1/tables/table_fmf_scenario_1.xlsx
@@ -479,37 +479,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30416.6 ± 9.8</t>
+          <t>50720.6 ± 17.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25325.2 ± 19.9</t>
+          <t>42223.5 ± 34.9</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>122.6 ± 2.5</t>
+          <t>207.5 ± 5.6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12.0 ± 0.7</t>
+          <t>18.8 ± 1.4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>54.6 ± 1.1</t>
+          <t>97.0 ± 3.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>30.2 ± 2.6</t>
+          <t>50.8 ± 2.1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.0 ± 0.6</t>
+          <t>2.7 ± 0.5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -534,37 +534,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30829.2 ± 20.3</t>
+          <t>51390.1 ± 18.2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>25617.0 ± 11.2</t>
+          <t>42702.8 ± 39.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>127.0 ± 2.8</t>
+          <t>211.7 ± 5.8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12.6 ± 0.8</t>
+          <t>19.3 ± 1.4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>58.0 ± 1.4</t>
+          <t>99.8 ± 3.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>30.6 ± 2.4</t>
+          <t>51.8 ± 2.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.0 ± 0.6</t>
+          <t>2.9 ± 0.5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -589,37 +589,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31345.4 ± 25.8</t>
+          <t>52229.6 ± 22.5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26019.4 ± 27.0</t>
+          <t>43359.2 ± 43.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>128.0 ± 3.0</t>
+          <t>214.9 ± 5.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12.8 ± 0.7</t>
+          <t>19.1 ± 1.5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>59.2 ± 1.8</t>
+          <t>102.2 ± 3.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>30.2 ± 2.4</t>
+          <t>52.9 ± 2.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.0 ± 0.6</t>
+          <t>2.9 ± 0.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -644,37 +644,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31858.0 ± 25.1</t>
+          <t>53088.3 ± 31.9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26427.6 ± 22.8</t>
+          <t>44027.8 ± 48.4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>131.8 ± 2.8</t>
+          <t>217.7 ± 5.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13.4 ± 0.6</t>
+          <t>19.3 ± 1.4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.8 ± 1.9</t>
+          <t>104.4 ± 3.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>32.0 ± 2.3</t>
+          <t>53.1 ± 2.1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.0 ± 0.6</t>
+          <t>2.9 ± 0.6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -699,37 +699,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>32405.0 ± 28.6</t>
+          <t>53979.4 ± 37.1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26845.4 ± 23.0</t>
+          <t>44739.2 ± 54.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>132.6 ± 3.0</t>
+          <t>223.8 ± 5.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14.0 ± 0.9</t>
+          <t>20.1 ± 1.6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.6 ± 2.1</t>
+          <t>108.5 ± 3.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>31.4 ± 2.3</t>
+          <t>54.5 ± 1.9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.0 ± 0.6</t>
+          <t>3.0 ± 0.6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -754,37 +754,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32958.6 ± 34.8</t>
+          <t>54895.6 ± 40.5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>27244.6 ± 29.2</t>
+          <t>45389.8 ± 58.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>134.0 ± 3.3</t>
+          <t>228.1 ± 5.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.2 ± 0.8</t>
+          <t>20.1 ± 1.7</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.8 ± 2.1</t>
+          <t>112.2 ± 3.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>32.2 ± 2.4</t>
+          <t>55.0 ± 1.9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.2 ± 0.6</t>
+          <t>3.0 ± 0.6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -809,37 +809,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>33504.4 ± 30.3</t>
+          <t>55830.1 ± 45.8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>27639.8 ± 21.8</t>
+          <t>46048.8 ± 66.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>135.6 ± 3.5</t>
+          <t>233.1 ± 5.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14.2 ± 0.9</t>
+          <t>20.1 ± 1.8</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>63.0 ± 2.0</t>
+          <t>116.5 ± 3.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>32.6 ± 2.4</t>
+          <t>55.8 ± 2.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.2 ± 0.6</t>
+          <t>3.0 ± 0.6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -864,37 +864,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>34050.4 ± 39.7</t>
+          <t>56758.3 ± 46.6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>28026.0 ± 34.2</t>
+          <t>46720.3 ± 65.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>139.0 ± 2.9</t>
+          <t>237.6 ± 5.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14.6 ± 1.0</t>
+          <t>21.2 ± 1.9</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.8 ± 1.7</t>
+          <t>119.5 ± 3.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>33.4 ± 2.7</t>
+          <t>56.4 ± 1.9</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.0 ± 0.5</t>
+          <t>2.9 ± 0.6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -919,37 +919,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>34605.4 ± 45.1</t>
+          <t>57718.4 ± 46.8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>28408.2 ± 38.4</t>
+          <t>47426.4 ± 65.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>143.2 ± 3.8</t>
+          <t>241.7 ± 5.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15.4 ± 1.2</t>
+          <t>21.9 ± 1.8</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>67.6 ± 1.6</t>
+          <t>122.1 ± 3.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>34.4 ± 3.0</t>
+          <t>57.3 ± 1.9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.6 ± 0.3</t>
+          <t>2.9 ± 0.6</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -974,37 +974,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>35165.4 ± 53.1</t>
+          <t>58669.4 ± 48.8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>28799.2 ± 48.2</t>
+          <t>48104.8 ± 67.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>143.6 ± 3.4</t>
+          <t>246.9 ± 5.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16.2 ± 1.1</t>
+          <t>22.9 ± 1.8</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>68.2 ± 1.8</t>
+          <t>124.9 ± 3.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>33.6 ± 2.8</t>
+          <t>58.8 ± 2.1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.6 ± 0.3</t>
+          <t>2.9 ± 0.6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1029,37 +1029,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>35659.6 ± 43.1</t>
+          <t>59478.8 ± 51.2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>29142.8 ± 36.5</t>
+          <t>48639.3 ± 69.7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>146.0 ± 2.2</t>
+          <t>249.1 ± 4.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16.8 ± 1.1</t>
+          <t>22.4 ± 1.6</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.0 ± 1.6</t>
+          <t>127.8 ± 3.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>33.4 ± 2.2</t>
+          <t>58.9 ± 2.1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.0 ± 0.4</t>
+          <t>2.8 ± 0.7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1084,37 +1084,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>36083.4 ± 48.8</t>
+          <t>60237.3 ± 58.1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>29428.8 ± 44.2</t>
+          <t>49162.6 ± 72.7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>147.6 ± 2.1</t>
+          <t>252.4 ± 4.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17.0 ± 0.9</t>
+          <t>22.4 ± 1.7</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70.2 ± 1.1</t>
+          <t>130.8 ± 3.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>34.4 ± 2.4</t>
+          <t>59.2 ± 2.1</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.2 ± 0.3</t>
+          <t>3.0 ± 0.7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1139,37 +1139,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>36523.0 ± 47.5</t>
+          <t>60986.4 ± 62.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>29719.8 ± 36.2</t>
+          <t>49644.8 ± 72.3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>149.6 ± 1.1</t>
+          <t>256.0 ± 4.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17.8 ± 0.9</t>
+          <t>22.7 ± 1.7</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>70.8 ± 1.7</t>
+          <t>133.6 ± 3.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>35.2 ± 2.1</t>
+          <t>59.8 ± 2.3</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.0 ± 0.3</t>
+          <t>3.1 ± 0.6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1194,37 +1194,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>36938.8 ± 52.0</t>
+          <t>61746.4 ± 64.9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>29982.6 ± 34.1</t>
+          <t>50129.3 ± 75.8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>151.2 ± 0.9</t>
+          <t>258.2 ± 4.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18.0 ± 0.8</t>
+          <t>23.2 ± 1.7</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>72.4 ± 1.7</t>
+          <t>134.7 ± 3.7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>35.0 ± 2.1</t>
+          <t>60.2 ± 2.3</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.0 ± 0.3</t>
+          <t>3.3 ± 0.6</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1249,37 +1249,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>37374.8 ± 51.5</t>
+          <t>62499.4 ± 69.7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>30238.6 ± 38.8</t>
+          <t>50586.3 ± 79.6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>152.2 ± 1.3</t>
+          <t>261.0 ± 4.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18.2 ± 1.3</t>
+          <t>23.1 ± 1.8</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>73.2 ± 1.9</t>
+          <t>137.7 ± 3.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>35.4 ± 2.4</t>
+          <t>60.0 ± 2.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.8 ± 0.2</t>
+          <t>3.5 ± 0.7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1304,37 +1304,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>37816.6 ± 61.3</t>
+          <t>63260.1 ± 72.7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>30511.6 ± 55.3</t>
+          <t>51061.0 ± 79.4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>156.4 ± 1.1</t>
+          <t>264.3 ± 4.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18.6 ± 0.9</t>
+          <t>23.6 ± 1.6</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>74.6 ± 2.3</t>
+          <t>139.5 ± 3.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>38.0 ± 1.7</t>
+          <t>60.8 ± 1.9</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.8 ± 0.4</t>
+          <t>3.6 ± 0.7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1359,37 +1359,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>38249.2 ± 54.3</t>
+          <t>64014.1 ± 75.0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>30757.0 ± 57.8</t>
+          <t>51522.7 ± 85.8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>158.2 ± 0.9</t>
+          <t>267.6 ± 4.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>19.2 ± 0.8</t>
+          <t>23.9 ± 1.7</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>75.4 ± 3.1</t>
+          <t>141.5 ± 3.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>39.2 ± 1.7</t>
+          <t>61.9 ± 1.8</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.4 ± 0.4</t>
+          <t>3.5 ± 0.8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1414,37 +1414,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>38697.0 ± 46.3</t>
+          <t>64764.6 ± 78.1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>31024.4 ± 52.1</t>
+          <t>51984.8 ± 88.8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>158.6 ± 1.2</t>
+          <t>271.4 ± 4.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19.2 ± 1.0</t>
+          <t>24.8 ± 1.6</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>76.2 ± 3.5</t>
+          <t>143.0 ± 3.9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>39.0 ± 1.8</t>
+          <t>63.1 ± 1.8</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.2 ± 0.3</t>
+          <t>3.8 ± 0.8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1469,37 +1469,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>39150.6 ± 49.9</t>
+          <t>65530.8 ± 78.5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>31298.4 ± 52.0</t>
+          <t>52434.7 ± 83.3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>161.8 ± 1.9</t>
+          <t>274.8 ± 4.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>18.4 ± 1.0</t>
+          <t>25.6 ± 1.6</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>79.0 ± 3.2</t>
+          <t>145.2 ± 3.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>40.2 ± 1.5</t>
+          <t>63.7 ± 2.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.2 ± 0.3</t>
+          <t>3.6 ± 0.8</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1524,37 +1524,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>39605.0 ± 54.3</t>
+          <t>66288.1 ± 76.5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>31563.8 ± 54.9</t>
+          <t>52889.3 ± 86.4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>163.2 ± 2.0</t>
+          <t>278.1 ± 4.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18.4 ± 1.2</t>
+          <t>26.3 ± 1.7</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>79.4 ± 3.0</t>
+          <t>146.9 ± 4.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>41.2 ± 1.5</t>
+          <t>64.8 ± 2.1</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.4 ± 0.4</t>
+          <t>3.5 ± 0.8</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1579,37 +1579,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>40040.2 ± 52.6</t>
+          <t>67025.8 ± 77.8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>31778.0 ± 53.0</t>
+          <t>53228.8 ± 87.4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>164.4 ± 2.3</t>
+          <t>281.4 ± 4.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17.4 ± 1.0</t>
+          <t>26.6 ± 1.9</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>81.4 ± 3.2</t>
+          <t>148.6 ± 4.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>41.4 ± 1.5</t>
+          <t>66.0 ± 2.4</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.4 ± 0.4</t>
+          <t>3.7 ± 0.8</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1634,37 +1634,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>40446.8 ± 49.9</t>
+          <t>67752.2 ± 76.6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>31970.8 ± 46.2</t>
+          <t>53594.8 ± 86.7</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>166.4 ± 1.4</t>
+          <t>285.6 ± 4.5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17.4 ± 1.0</t>
+          <t>26.8 ± 1.9</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>82.4 ± 2.2</t>
+          <t>151.4 ± 4.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>42.2 ± 1.6</t>
+          <t>67.5 ± 2.4</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.8 ± 0.4</t>
+          <t>3.7 ± 0.9</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1689,37 +1689,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>40873.8 ± 44.0</t>
+          <t>68469.6 ± 78.0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>32199.6 ± 50.5</t>
+          <t>53958.9 ± 96.1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>167.2 ± 1.9</t>
+          <t>287.9 ± 5.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17.4 ± 1.0</t>
+          <t>26.6 ± 1.9</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>83.2 ± 2.4</t>
+          <t>152.9 ± 4.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>42.6 ± 1.6</t>
+          <t>68.4 ± 2.3</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.8 ± 0.4</t>
+          <t>3.9 ± 0.9</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1744,37 +1744,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>41293.0 ± 42.3</t>
+          <t>69178.0 ± 79.7</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>32418.0 ± 46.2</t>
+          <t>54316.5 ± 93.4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>167.4 ± 3.0</t>
+          <t>290.4 ± 5.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17.6 ± 1.1</t>
+          <t>26.6 ± 1.9</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>83.4 ± 2.2</t>
+          <t>154.6 ± 4.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>42.2 ± 2.2</t>
+          <t>69.1 ± 2.5</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.0 ± 0.5</t>
+          <t>4.0 ± 0.9</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1799,37 +1799,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>41705.0 ± 44.8</t>
+          <t>69886.4 ± 80.6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>32643.2 ± 42.6</t>
+          <t>54676.1 ± 89.9</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>171.0 ± 2.9</t>
+          <t>293.7 ± 5.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>18.6 ± 1.3</t>
+          <t>27.1 ± 1.7</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>86.0 ± 2.2</t>
+          <t>156.6 ± 4.3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>42.2 ± 2.2</t>
+          <t>69.9 ± 2.6</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.0 ± 0.5</t>
+          <t>4.0 ± 0.9</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1854,37 +1854,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>42129.8 ± 48.7</t>
+          <t>70578.3 ± 85.9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>32863.4 ± 56.6</t>
+          <t>55032.4 ± 94.3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>171.8 ± 3.1</t>
+          <t>296.2 ± 5.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18.4 ± 1.5</t>
+          <t>27.3 ± 1.8</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>86.8 ± 3.0</t>
+          <t>157.9 ± 4.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>42.6 ± 2.2</t>
+          <t>71.0 ± 2.4</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.0 ± 0.5</t>
+          <t>4.0 ± 0.9</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1909,37 +1909,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>42517.6 ± 48.9</t>
+          <t>71273.7 ± 87.2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>33079.4 ± 52.4</t>
+          <t>55402.7 ± 96.3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>173.2 ± 2.6</t>
+          <t>298.5 ± 5.6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18.4 ± 1.6</t>
+          <t>27.5 ± 1.7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>87.4 ± 2.6</t>
+          <t>159.1 ± 4.4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>43.6 ± 2.3</t>
+          <t>71.9 ± 2.8</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.0 ± 0.5</t>
+          <t>4.0 ± 0.9</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1964,37 +1964,37 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>42918.4 ± 52.5</t>
+          <t>71953.4 ± 84.0</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>33284.6 ± 57.2</t>
+          <t>55769.9 ± 97.8</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>175.6 ± 2.3</t>
+          <t>301.1 ± 5.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19.0 ± 1.5</t>
+          <t>28.4 ± 1.6</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>88.0 ± 3.0</t>
+          <t>159.7 ± 4.6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>44.8 ± 2.0</t>
+          <t>73.0 ± 2.9</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.0 ± 0.5</t>
+          <t>4.2 ± 0.9</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2019,37 +2019,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>43284.6 ± 61.7</t>
+          <t>72613.6 ± 87.5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>33467.0 ± 66.8</t>
+          <t>56133.6 ± 102.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>178.0 ± 2.4</t>
+          <t>303.1 ± 5.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>18.8 ± 1.1</t>
+          <t>28.6 ± 1.7</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>89.8 ± 2.7</t>
+          <t>161.4 ± 5.0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>45.4 ± 2.2</t>
+          <t>73.0 ± 2.7</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.2 ± 0.6</t>
+          <t>4.3 ± 0.8</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2074,37 +2074,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>43673.8 ± 72.3</t>
+          <t>73244.9 ± 97.0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>33692.8 ± 80.8</t>
+          <t>56476.3 ± 109.6</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>182.4 ± 3.4</t>
+          <t>306.6 ± 5.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19.4 ± 0.9</t>
+          <t>29.1 ± 2.0</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>92.8 ± 2.6</t>
+          <t>163.4 ± 4.6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>46.6 ± 2.5</t>
+          <t>74.0 ± 2.9</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.2 ± 0.6</t>
+          <t>4.3 ± 0.7</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2129,37 +2129,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>44064.6 ± 75.0</t>
+          <t>73868.2 ± 101.8</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>33894.0 ± 87.9</t>
+          <t>56816.3 ± 109.4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>184.4 ± 3.7</t>
+          <t>310.5 ± 5.8</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20.2 ± 1.1</t>
+          <t>29.5 ± 1.8</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>93.8 ± 2.0</t>
+          <t>166.2 ± 4.9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>46.6 ± 2.6</t>
+          <t>74.8 ± 3.2</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.4 ± 0.7</t>
+          <t>4.5 ± 0.7</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2184,37 +2184,37 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>44437.2 ± 73.4</t>
+          <t>74473.6 ± 108.0</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>34121.0 ± 83.7</t>
+          <t>57186.0 ± 112.6</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>185.4 ± 3.9</t>
+          <t>313.4 ± 5.8</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20.0 ± 1.0</t>
+          <t>30.1 ± 1.8</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>94.8 ± 1.9</t>
+          <t>167.4 ± 5.1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>47.2 ± 2.7</t>
+          <t>75.7 ± 3.1</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.0 ± 0.7</t>
+          <t>4.6 ± 0.7</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2239,37 +2239,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>44813.8 ± 80.0</t>
+          <t>75095.7 ± 110.0</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>34365.4 ± 86.0</t>
+          <t>57554.4 ± 114.7</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>188.0 ± 4.3</t>
+          <t>312.9 ± 5.6</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20.2 ± 0.9</t>
+          <t>30.7 ± 1.9</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>96.8 ± 2.1</t>
+          <t>169.4 ± 5.2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>48.4 ± 2.7</t>
+          <t>75.8 ± 3.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2.8 ± 0.7</t>
+          <t>4.7 ± 0.6</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2294,37 +2294,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>45191.8 ± 85.2</t>
+          <t>75773.8 ± 123.3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>34604.2 ± 88.6</t>
+          <t>57994.5 ± 126.9</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>187.6 ± 4.0</t>
+          <t>314.0 ± 6.1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>21.0 ± 1.2</t>
+          <t>31.6 ± 2.0</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>97.8 ± 1.9</t>
+          <t>171.5 ± 5.1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>48.6 ± 2.6</t>
+          <t>77.2 ± 3.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3.0 ± 0.7</t>
+          <t>4.7 ± 0.7</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2349,37 +2349,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>45605.2 ± 81.9</t>
+          <t>76486.4 ± 134.6</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>34861.4 ± 85.0</t>
+          <t>58480.1 ± 136.5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>187.4 ± 3.7</t>
+          <t>315.2 ± 6.3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>21.4 ± 1.4</t>
+          <t>32.2 ± 2.0</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>98.8 ± 1.8</t>
+          <t>173.8 ± 5.1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>48.6 ± 2.4</t>
+          <t>78.0 ± 3.1</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.0 ± 0.7</t>
+          <t>4.8 ± 0.7</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2404,37 +2404,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>46044.8 ± 83.8</t>
+          <t>77204.6 ± 147.7</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>35110.6 ± 80.2</t>
+          <t>58897.3 ± 150.2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>186.6 ± 4.2</t>
+          <t>317.6 ± 6.6</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>21.0 ± 1.3</t>
+          <t>32.9 ± 2.1</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>100.2 ± 2.5</t>
+          <t>176.1 ± 5.2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>48.8 ± 2.4</t>
+          <t>79.3 ± 3.1</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.8 ± 0.6</t>
+          <t>4.8 ± 0.7</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2459,37 +2459,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>46449.8 ± 88.8</t>
+          <t>77903.3 ± 153.8</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>35357.8 ± 82.3</t>
+          <t>59330.8 ± 154.9</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>186.6 ± 4.5</t>
+          <t>316.4 ± 6.4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>21.8 ± 1.3</t>
+          <t>33.1 ± 2.3</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>102.0 ± 2.4</t>
+          <t>177.4 ± 5.6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>48.2 ± 2.4</t>
+          <t>80.0 ± 3.3</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3.0 ± 0.5</t>
+          <t>5.0 ± 0.8</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2514,37 +2514,37 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>46840.6 ± 88.6</t>
+          <t>78592.1 ± 157.6</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>35596.8 ± 78.7</t>
+          <t>59759.2 ± 159.1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>185.4 ± 4.9</t>
+          <t>317.1 ± 6.6</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>22.4 ± 1.4</t>
+          <t>33.5 ± 2.3</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>101.6 ± 2.6</t>
+          <t>179.2 ± 5.7</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>48.2 ± 2.7</t>
+          <t>80.1 ± 3.4</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2.6 ± 0.3</t>
+          <t>5.0 ± 0.8</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2569,37 +2569,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>46933.8 ± 105.0</t>
+          <t>78742.6 ± 160.6</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>35787.4 ± 95.2</t>
+          <t>60044.9 ± 161.6</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>186.4 ± 4.9</t>
+          <t>317.4 ± 6.5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>23.0 ± 1.2</t>
+          <t>33.9 ± 2.2</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>102.8 ± 3.2</t>
+          <t>180.4 ± 5.7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>49.8 ± 2.6</t>
+          <t>81.4 ± 3.4</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2.6 ± 0.3</t>
+          <t>4.9 ± 0.9</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2624,37 +2624,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>47342.0 ± 99.6</t>
+          <t>79443.9 ± 162.8</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>36049.6 ± 93.0</t>
+          <t>60493.8 ± 164.8</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>186.4 ± 4.6</t>
+          <t>317.4 ± 7.1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>23.0 ± 1.2</t>
+          <t>34.5 ± 2.3</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>103.0 ± 2.9</t>
+          <t>181.5 ± 6.0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>50.8 ± 2.5</t>
+          <t>82.0 ± 3.5</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2.8 ± 0.3</t>
+          <t>5.0 ± 0.9</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2679,37 +2679,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>47756.4 ± 99.6</t>
+          <t>80139.2 ± 165.8</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>36260.6 ± 93.0</t>
+          <t>60870.4 ± 165.5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>185.4 ± 4.6</t>
+          <t>316.2 ± 7.5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>22.6 ± 1.3</t>
+          <t>35.1 ± 2.4</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>103.8 ± 2.5</t>
+          <t>182.2 ± 6.2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>51.0 ± 2.8</t>
+          <t>82.2 ± 3.3</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2.8 ± 0.3</t>
+          <t>5.1 ± 0.9</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2734,37 +2734,37 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>48110.8 ± 87.7</t>
+          <t>80762.0 ± 168.4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>36450.0 ± 82.7</t>
+          <t>61198.6 ± 165.7</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>185.4 ± 4.5</t>
+          <t>314.9 ± 7.3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>22.4 ± 1.4</t>
+          <t>35.5 ± 2.4</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>104.2 ± 3.0</t>
+          <t>182.3 ± 5.9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>51.8 ± 2.7</t>
+          <t>82.6 ± 3.2</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2.8 ± 0.3</t>
+          <t>5.2 ± 0.9</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2789,37 +2789,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>48414.2 ± 99.9</t>
+          <t>81290.2 ± 172.0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>36564.8 ± 101.3</t>
+          <t>61435.6 ± 164.9</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>188.0 ± 4.6</t>
+          <t>314.4 ± 7.2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>22.6 ± 1.6</t>
+          <t>36.0 ± 2.5</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>106.0 ± 3.4</t>
+          <t>183.4 ± 5.8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>52.8 ± 2.3</t>
+          <t>82.9 ± 3.1</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2.8 ± 0.3</t>
+          <t>5.1 ± 1.0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2844,37 +2844,37 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>48659.2 ± 105.4</t>
+          <t>81710.4 ± 179.1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>36644.2 ± 105.1</t>
+          <t>61578.4 ± 171.3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>190.6 ± 4.9</t>
+          <t>314.5 ± 7.7</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>22.6 ± 1.9</t>
+          <t>36.5 ± 2.6</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>108.0 ± 3.4</t>
+          <t>184.8 ± 6.0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>54.4 ± 2.4</t>
+          <t>83.0 ± 3.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2.8 ± 0.3</t>
+          <t>5.0 ± 1.0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2899,37 +2899,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>48833.2 ± 101.8</t>
+          <t>82000.4 ± 181.2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>36655.8 ± 101.7</t>
+          <t>61612.3 ± 175.2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>188.4 ± 5.7</t>
+          <t>313.1 ± 7.7</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>22.8 ± 2.0</t>
+          <t>36.5 ± 2.6</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>107.4 ± 4.1</t>
+          <t>184.7 ± 6.2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>53.4 ± 2.2</t>
+          <t>83.2 ± 3.1</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2.8 ± 0.3</t>
+          <t>5.0 ± 1.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2954,37 +2954,37 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>48996.8 ± 107.7</t>
+          <t>82282.6 ± 186.5</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>36584.2 ± 108.8</t>
+          <t>61466.1 ± 178.0</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>187.8 ± 5.8</t>
+          <t>312.6 ± 7.5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>22.8 ± 1.9</t>
+          <t>36.6 ± 2.5</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>108.0 ± 3.3</t>
+          <t>185.0 ± 6.0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>53.2 ± 2.4</t>
+          <t>83.1 ± 3.2</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2.8 ± 0.3</t>
+          <t>5.2 ± 0.9</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3009,37 +3009,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>49137.4 ± 119.9</t>
+          <t>82521.9 ± 186.2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>36456.2 ± 117.8</t>
+          <t>61307.8 ± 180.0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>187.6 ± 6.6</t>
+          <t>309.9 ± 7.2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>23.0 ± 2.3</t>
+          <t>36.8 ± 2.4</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>108.0 ± 3.5</t>
+          <t>183.8 ± 5.6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>53.6 ± 2.7</t>
+          <t>82.6 ± 3.2</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2.6 ± 0.2</t>
+          <t>5.3 ± 1.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3064,37 +3064,37 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>49233.0 ± 117.2</t>
+          <t>82675.4 ± 189.7</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>36300.4 ± 116.6</t>
+          <t>61074.2 ± 180.7</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>186.8 ± 6.5</t>
+          <t>308.4 ± 7.3</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>22.6 ± 2.6</t>
+          <t>36.5 ± 2.5</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>107.2 ± 3.0</t>
+          <t>183.3 ± 5.4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>54.4 ± 2.7</t>
+          <t>83.0 ± 3.4</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2.6 ± 0.2</t>
+          <t>5.2 ± 1.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3119,37 +3119,37 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>49271.2 ± 121.6</t>
+          <t>82758.4 ± 196.9</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>36135.4 ± 110.7</t>
+          <t>60789.2 ± 181.6</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>187.2 ± 6.5</t>
+          <t>306.9 ± 6.6</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>22.6 ± 2.4</t>
+          <t>36.1 ± 2.3</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>107.6 ± 3.2</t>
+          <t>183.3 ± 4.9</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>54.4 ± 2.6</t>
+          <t>82.5 ± 3.3</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2.6 ± 0.2</t>
+          <t>4.9 ± 0.9</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3174,37 +3174,37 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>49222.2 ± 131.8</t>
+          <t>82695.7 ± 200.1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>35856.0 ± 111.7</t>
+          <t>60367.2 ± 187.1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>190.8 ± 6.6</t>
+          <t>306.6 ± 6.7</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>22.4 ± 2.7</t>
+          <t>36.0 ± 2.4</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>109.4 ± 3.1</t>
+          <t>182.5 ± 4.9</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>56.6 ± 2.8</t>
+          <t>83.0 ± 3.2</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2.4 ± 0.2</t>
+          <t>5.0 ± 0.8</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3229,37 +3229,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>49152.8 ± 132.1</t>
+          <t>82572.4 ± 200.2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>35573.4 ± 105.2</t>
+          <t>59874.2 ± 183.7</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>193.0 ± 5.7</t>
+          <t>306.6 ± 6.8</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>23.2 ± 2.9</t>
+          <t>35.7 ± 2.2</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>108.8 ± 3.0</t>
+          <t>181.8 ± 4.7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>58.8 ± 2.2</t>
+          <t>84.3 ± 3.2</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2.2 ± 0.2</t>
+          <t>4.8 ± 0.8</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3284,37 +3284,37 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>49066.4 ± 129.9</t>
+          <t>82387.5 ± 201.8</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>35301.6 ± 110.2</t>
+          <t>59384.0 ± 185.2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>192.6 ± 5.3</t>
+          <t>306.6 ± 7.1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>22.6 ± 2.7</t>
+          <t>35.3 ± 2.3</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>108.6 ± 2.8</t>
+          <t>181.2 ± 5.0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>59.0 ± 1.9</t>
+          <t>85.1 ± 3.3</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2.4 ± 0.2</t>
+          <t>4.9 ± 0.8</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3339,37 +3339,37 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>48916.2 ± 123.2</t>
+          <t>82165.5 ± 208.3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>34898.2 ± 110.8</t>
+          <t>58749.2 ± 186.2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>193.4 ± 5.7</t>
+          <t>305.1 ± 6.6</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>23.4 ± 2.6</t>
+          <t>35.2 ± 2.4</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>108.4 ± 3.2</t>
+          <t>179.7 ± 4.3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>59.2 ± 1.8</t>
+          <t>85.5 ± 3.3</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2.4 ± 0.2</t>
+          <t>4.8 ± 0.8</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3394,37 +3394,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>48800.4 ± 130.8</t>
+          <t>81975.4 ± 214.2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>34545.2 ± 117.0</t>
+          <t>58151.9 ± 192.1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>192.6 ± 5.5</t>
+          <t>302.4 ± 6.3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>23.4 ± 2.6</t>
+          <t>35.2 ± 2.3</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>107.4 ± 3.2</t>
+          <t>177.3 ± 4.3</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>59.0 ± 1.4</t>
+          <t>85.0 ± 3.2</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2.8 ± 0.3</t>
+          <t>4.9 ± 0.8</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3449,37 +3449,37 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>48735.0 ± 124.3</t>
+          <t>81847.0 ± 214.8</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>34220.8 ± 114.2</t>
+          <t>57596.5 ± 192.4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>192.2 ± 5.4</t>
+          <t>300.6 ± 6.4</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>22.8 ± 2.6</t>
+          <t>35.0 ± 2.2</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>108.0 ± 3.3</t>
+          <t>175.7 ± 4.2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>58.6 ± 2.0</t>
+          <t>85.2 ± 3.6</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2.8 ± 0.5</t>
+          <t>4.8 ± 0.9</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3504,37 +3504,37 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>48606.8 ± 131.9</t>
+          <t>81629.9 ± 211.8</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>33827.0 ± 121.3</t>
+          <t>56955.2 ± 188.5</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>193.2 ± 6.2</t>
+          <t>297.3 ± 6.5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>23.0 ± 2.5</t>
+          <t>34.5 ± 2.2</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>108.4 ± 3.6</t>
+          <t>172.9 ± 4.3</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>59.0 ± 3.0</t>
+          <t>85.0 ± 3.4</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2.8 ± 0.5</t>
+          <t>4.8 ± 0.9</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3559,37 +3559,37 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>48432.4 ± 130.4</t>
+          <t>81364.5 ± 204.8</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>33430.4 ± 125.9</t>
+          <t>56307.0 ± 185.0</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>192.6 ± 5.7</t>
+          <t>294.6 ± 6.6</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>22.4 ± 2.1</t>
+          <t>34.5 ± 2.1</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>107.6 ± 3.2</t>
+          <t>170.9 ± 4.3</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>60.0 ± 2.7</t>
+          <t>84.2 ± 3.5</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2.6 ± 0.5</t>
+          <t>5.0 ± 0.9</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3614,37 +3614,37 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>48320.6 ± 128.2</t>
+          <t>81172.2 ± 199.7</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>33085.4 ± 121.7</t>
+          <t>55744.1 ± 181.7</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>189.4 ± 5.9</t>
+          <t>292.0 ± 6.7</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>23.0 ± 1.7</t>
+          <t>34.3 ± 1.9</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>106.6 ± 2.9</t>
+          <t>169.3 ± 4.8</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>57.4 ± 3.2</t>
+          <t>83.4 ± 3.2</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2.4 ± 0.5</t>
+          <t>5.0 ± 0.9</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3669,37 +3669,37 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>48189.6 ± 124.9</t>
+          <t>80939.2 ± 191.0</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>32751.6 ± 122.9</t>
+          <t>55143.7 ± 179.7</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>187.2 ± 5.4</t>
+          <t>289.4 ± 6.3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>22.6 ± 1.6</t>
+          <t>34.3 ± 1.6</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>105.8 ± 2.9</t>
+          <t>167.1 ± 4.4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>56.8 ± 3.1</t>
+          <t>83.0 ± 3.3</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2.0 ± 0.3</t>
+          <t>5.0 ± 0.9</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3724,37 +3724,37 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>48078.4 ± 128.3</t>
+          <t>80775.8 ± 193.2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>32458.0 ± 117.9</t>
+          <t>54632.4 ± 175.9</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>185.0 ± 5.3</t>
+          <t>285.2 ± 6.8</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>22.8 ± 1.4</t>
+          <t>33.5 ± 1.8</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>104.2 ± 3.0</t>
+          <t>164.9 ± 4.8</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>56.0 ± 3.0</t>
+          <t>81.9 ± 3.5</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2.0 ± 0.3</t>
+          <t>4.8 ± 0.9</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3779,37 +3779,37 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>47985.6 ± 142.1</t>
+          <t>80583.8 ± 196.6</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>32146.2 ± 135.4</t>
+          <t>54130.8 ± 174.0</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>184.0 ± 5.3</t>
+          <t>283.6 ± 7.4</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>23.0 ± 1.5</t>
+          <t>33.0 ± 1.8</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>103.6 ± 3.1</t>
+          <t>163.2 ± 4.9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>55.4 ± 2.6</t>
+          <t>82.4 ± 3.8</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2.0 ± 0.3</t>
+          <t>5.0 ± 0.9</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3834,37 +3834,37 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>47875.2 ± 142.8</t>
+          <t>80414.6 ± 202.2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>31890.2 ± 129.1</t>
+          <t>53653.8 ± 174.5</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>183.2 ± 4.3</t>
+          <t>279.1 ± 7.4</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>23.6 ± 1.7</t>
+          <t>33.0 ± 1.9</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>102.2 ± 2.5</t>
+          <t>160.3 ± 4.8</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>55.4 ± 2.6</t>
+          <t>81.0 ± 3.4</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2.0 ± 0.3</t>
+          <t>4.8 ± 0.8</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3889,37 +3889,37 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>47796.6 ± 154.9</t>
+          <t>80291.9 ± 196.0</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>31639.8 ± 143.6</t>
+          <t>53264.6 ± 169.5</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>182.2 ± 5.1</t>
+          <t>274.5 ± 7.3</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>23.8 ± 1.6</t>
+          <t>32.7 ± 1.8</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>100.2 ± 3.2</t>
+          <t>157.3 ± 5.0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>56.2 ± 2.5</t>
+          <t>79.7 ± 3.4</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2.0 ± 0.3</t>
+          <t>4.8 ± 0.8</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3944,37 +3944,37 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>47706.4 ± 155.1</t>
+          <t>80159.6 ± 197.2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>31424.0 ± 138.4</t>
+          <t>52877.8 ± 167.1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>180.8 ± 4.8</t>
+          <t>270.6 ± 7.5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>23.0 ± 1.4</t>
+          <t>31.8 ± 1.8</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>99.8 ± 2.8</t>
+          <t>155.2 ± 4.8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>55.6 ± 2.5</t>
+          <t>79.0 ± 3.3</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2.4 ± 0.3</t>
+          <t>4.8 ± 0.8</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3999,37 +3999,37 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>47634.2 ± 163.5</t>
+          <t>80059.9 ± 202.7</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>31241.6 ± 137.6</t>
+          <t>52588.5 ± 166.9</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>179.0 ± 4.9</t>
+          <t>268.3 ± 7.3</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>22.6 ± 1.2</t>
+          <t>31.9 ± 1.7</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>98.4 ± 2.7</t>
+          <t>153.9 ± 4.6</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>55.6 ± 2.6</t>
+          <t>77.8 ± 3.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2.4 ± 0.3</t>
+          <t>4.8 ± 0.9</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4054,37 +4054,37 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>47524.2 ± 158.6</t>
+          <t>79898.0 ± 201.0</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>31023.2 ± 126.4</t>
+          <t>52226.8 ± 164.6</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>176.0 ± 5.9</t>
+          <t>264.2 ± 7.9</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>21.4 ± 0.7</t>
+          <t>31.2 ± 1.8</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>97.4 ± 3.5</t>
+          <t>152.1 ± 4.9</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>54.6 ± 2.7</t>
+          <t>76.3 ± 3.1</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2.6 ± 0.3</t>
+          <t>4.6 ± 0.7</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4109,37 +4109,37 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>47426.2 ± 161.3</t>
+          <t>79695.1 ± 206.8</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>30841.2 ± 128.2</t>
+          <t>51856.8 ± 163.5</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>175.8 ± 5.7</t>
+          <t>260.2 ± 7.4</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>21.2 ± 0.9</t>
+          <t>31.0 ± 1.8</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>97.4 ± 3.6</t>
+          <t>149.6 ± 5.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>54.6 ± 2.5</t>
+          <t>75.2 ± 2.9</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2.6 ± 0.3</t>
+          <t>4.5 ± 0.7</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4164,37 +4164,37 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>47366.2 ± 155.6</t>
+          <t>79526.1 ± 206.5</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>30660.4 ± 136.7</t>
+          <t>51514.4 ± 162.9</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>172.8 ± 6.7</t>
+          <t>259.6 ± 7.6</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20.8 ± 1.0</t>
+          <t>31.1 ± 1.9</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>95.6 ± 3.8</t>
+          <t>149.5 ± 5.2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>54.0 ± 3.1</t>
+          <t>74.3 ± 3.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2.4 ± 0.3</t>
+          <t>4.6 ± 0.7</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4219,37 +4219,37 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>47252.6 ± 157.8</t>
+          <t>79359.8 ± 205.1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>30453.6 ± 138.9</t>
+          <t>51146.5 ± 163.1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>167.2 ± 7.3</t>
+          <t>255.6 ± 7.2</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>19.6 ± 1.0</t>
+          <t>30.8 ± 1.9</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>94.0 ± 3.8</t>
+          <t>147.3 ± 5.2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>51.2 ± 3.3</t>
+          <t>72.8 ± 2.9</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2.4 ± 0.3</t>
+          <t>4.7 ± 0.7</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4274,37 +4274,37 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>47123.8 ± 162.5</t>
+          <t>79146.0 ± 210.3</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>30224.0 ± 134.6</t>
+          <t>50767.8 ± 167.0</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>164.6 ± 6.8</t>
+          <t>253.2 ± 6.5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>19.6 ± 0.9</t>
+          <t>30.6 ± 1.8</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>91.8 ± 3.5</t>
+          <t>145.3 ± 4.8</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>51.0 ± 3.0</t>
+          <t>72.7 ± 2.9</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2.2 ± 0.3</t>
+          <t>4.7 ± 0.7</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4329,37 +4329,37 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>46845.0 ± 172.2</t>
+          <t>78623.1 ± 212.3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>30020.2 ± 143.5</t>
+          <t>50359.7 ± 168.8</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>162.6 ± 6.5</t>
+          <t>252.5 ± 6.7</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>19.2 ± 0.9</t>
+          <t>30.8 ± 1.8</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>90.6 ± 3.8</t>
+          <t>145.2 ± 5.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>50.4 ± 2.7</t>
+          <t>71.8 ± 3.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2.4 ± 0.3</t>
+          <t>4.7 ± 0.6</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4384,37 +4384,37 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>46551.4 ± 174.9</t>
+          <t>78109.4 ± 212.5</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>29757.4 ± 149.6</t>
+          <t>49917.6 ± 169.6</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>160.0 ± 5.7</t>
+          <t>248.4 ± 6.4</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>19.0 ± 1.2</t>
+          <t>30.1 ± 1.9</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>90.0 ± 3.8</t>
+          <t>142.8 ± 4.9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>48.6 ± 2.1</t>
+          <t>70.8 ± 2.8</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2.4 ± 0.2</t>
+          <t>4.7 ± 0.6</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4439,37 +4439,37 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>46369.2 ± 180.6</t>
+          <t>77810.3 ± 208.8</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>29507.2 ± 151.0</t>
+          <t>49508.1 ± 164.8</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>156.4 ± 5.4</t>
+          <t>245.9 ± 6.4</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>18.8 ± 1.1</t>
+          <t>29.6 ± 2.1</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>87.0 ± 3.7</t>
+          <t>141.9 ± 4.8</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>48.2 ± 2.0</t>
+          <t>69.8 ± 2.7</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2.4 ± 0.2</t>
+          <t>4.6 ± 0.6</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4494,37 +4494,37 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>46281.0 ± 178.6</t>
+          <t>77672.9 ± 212.4</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>29306.0 ± 154.8</t>
+          <t>49183.2 ± 163.7</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>158.2 ± 5.9</t>
+          <t>243.8 ± 6.1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>19.2 ± 0.7</t>
+          <t>29.6 ± 2.1</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>88.4 ± 4.2</t>
+          <t>141.1 ± 4.7</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>48.0 ± 2.0</t>
+          <t>68.9 ± 2.6</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2.6 ± 0.3</t>
+          <t>4.3 ± 0.6</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4549,37 +4549,37 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>46057.2 ± 180.5</t>
+          <t>77266.9 ± 210.5</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>29061.0 ± 152.0</t>
+          <t>48732.1 ± 162.4</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>157.0 ± 5.9</t>
+          <t>241.1 ± 6.2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>18.4 ± 0.7</t>
+          <t>29.1 ± 2.0</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>88.2 ± 4.1</t>
+          <t>138.7 ± 4.6</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>47.8 ± 2.3</t>
+          <t>68.9 ± 2.9</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2.6 ± 0.3</t>
+          <t>4.5 ± 0.6</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4604,37 +4604,37 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>45772.8 ± 177.7</t>
+          <t>76855.1 ± 210.6</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>28751.4 ± 140.7</t>
+          <t>48284.6 ± 160.7</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>153.6 ± 5.3</t>
+          <t>238.3 ± 6.3</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>18.0 ± 0.8</t>
+          <t>28.2 ± 1.8</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>86.2 ± 4.0</t>
+          <t>137.5 ± 4.8</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>46.8 ± 2.1</t>
+          <t>68.2 ± 2.7</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2.6 ± 0.3</t>
+          <t>4.4 ± 0.5</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4659,37 +4659,37 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>45489.8 ± 175.7</t>
+          <t>76372.0 ± 212.1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>28465.2 ± 139.3</t>
+          <t>47792.0 ± 160.5</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>152.2 ± 5.9</t>
+          <t>235.4 ± 6.6</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>17.8 ± 0.8</t>
+          <t>27.5 ± 1.8</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>85.4 ± 4.6</t>
+          <t>136.8 ± 4.8</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>46.8 ± 2.1</t>
+          <t>67.0 ± 2.7</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2.2 ± 0.4</t>
+          <t>4.0 ± 0.5</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4714,37 +4714,37 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>45166.2 ± 174.5</t>
+          <t>75886.2 ± 212.5</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>28155.8 ± 134.9</t>
+          <t>47292.9 ± 163.1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>150.2 ± 4.7</t>
+          <t>232.4 ± 6.4</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>18.2 ± 0.7</t>
+          <t>27.5 ± 1.5</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>84.4 ± 4.2</t>
+          <t>135.0 ± 4.6</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>45.2 ± 1.9</t>
+          <t>65.8 ± 2.7</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2.4 ± 0.4</t>
+          <t>4.2 ± 0.7</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4769,37 +4769,37 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>44845.4 ± 170.3</t>
+          <t>75359.8 ± 208.1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>27869.6 ± 126.6</t>
+          <t>46782.2 ± 160.5</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>147.2 ± 4.4</t>
+          <t>230.1 ± 5.8</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>17.6 ± 0.9</t>
+          <t>27.2 ± 1.4</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>83.0 ± 4.3</t>
+          <t>133.0 ± 4.2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>44.2 ± 1.4</t>
+          <t>65.8 ± 2.5</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2.4 ± 0.4</t>
+          <t>4.0 ± 0.6</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4824,37 +4824,37 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>44513.6 ± 166.5</t>
+          <t>74821.9 ± 210.2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>27552.6 ± 116.6</t>
+          <t>46272.6 ± 163.9</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>145.6 ± 4.5</t>
+          <t>227.3 ± 6.0</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>17.8 ± 1.0</t>
+          <t>27.1 ± 1.3</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>82.4 ± 4.2</t>
+          <t>130.8 ± 4.4</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>43.0 ± 1.0</t>
+          <t>65.5 ± 2.6</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2.4 ± 0.4</t>
+          <t>4.0 ± 0.6</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4879,37 +4879,37 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>44205.8 ± 162.1</t>
+          <t>74258.6 ± 210.2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>27239.6 ± 116.7</t>
+          <t>45733.5 ± 164.2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>142.4 ± 4.5</t>
+          <t>225.9 ± 5.9</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>17.2 ± 1.2</t>
+          <t>27.2 ± 1.2</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>80.2 ± 4.6</t>
+          <t>130.7 ± 4.6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>42.4 ± 0.8</t>
+          <t>64.2 ± 2.6</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2.6 ± 0.4</t>
+          <t>3.9 ± 0.6</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4934,37 +4934,37 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>43841.0 ± 154.0</t>
+          <t>73626.2 ± 209.2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>26899.0 ± 125.0</t>
+          <t>45169.9 ± 158.0</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>140.2 ± 4.2</t>
+          <t>223.4 ± 5.8</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>18.0 ± 1.1</t>
+          <t>26.9 ± 1.3</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>79.0 ± 4.4</t>
+          <t>128.4 ± 4.3</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>40.8 ± 0.8</t>
+          <t>64.3 ± 2.6</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2.4 ± 0.4</t>
+          <t>3.8 ± 0.7</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4989,37 +4989,37 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>43454.4 ± 149.7</t>
+          <t>72972.4 ± 206.4</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>26529.2 ± 117.9</t>
+          <t>44585.6 ± 155.4</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>139.4 ± 5.0</t>
+          <t>221.3 ± 5.6</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>18.2 ± 1.0</t>
+          <t>26.6 ± 1.4</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>78.4 ± 4.9</t>
+          <t>127.2 ± 4.3</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>40.4 ± 0.5</t>
+          <t>63.5 ± 2.9</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2.4 ± 0.4</t>
+          <t>4.0 ± 0.7</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5044,37 +5044,37 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>43053.6 ± 154.1</t>
+          <t>72345.4 ± 199.4</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>26159.4 ± 125.4</t>
+          <t>43945.3 ± 145.6</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>139.4 ± 4.7</t>
+          <t>218.6 ± 5.5</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>17.8 ± 0.7</t>
+          <t>26.5 ± 1.4</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>78.6 ± 5.0</t>
+          <t>125.5 ± 4.3</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>40.6 ± 0.7</t>
+          <t>62.5 ± 3.0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2.4 ± 0.4</t>
+          <t>4.0 ± 0.8</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5099,37 +5099,37 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>42686.2 ± 151.2</t>
+          <t>71705.6 ± 194.5</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>25779.0 ± 127.2</t>
+          <t>43275.8 ± 140.0</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>137.4 ± 4.3</t>
+          <t>215.2 ± 6.0</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>17.6 ± 0.7</t>
+          <t>25.8 ± 1.4</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>77.8 ± 5.2</t>
+          <t>123.9 ± 4.6</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>39.6 ± 0.9</t>
+          <t>61.5 ± 3.1</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2.4 ± 0.4</t>
+          <t>4.1 ± 0.8</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5154,37 +5154,37 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>42314.0 ± 170.0</t>
+          <t>71067.6 ± 196.7</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>25358.4 ± 129.4</t>
+          <t>42587.9 ± 141.5</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>132.6 ± 3.7</t>
+          <t>211.2 ± 5.5</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>16.4 ± 0.8</t>
+          <t>25.6 ± 1.5</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>75.2 ± 5.2</t>
+          <t>121.5 ± 4.6</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>38.8 ± 1.4</t>
+          <t>60.0 ± 2.6</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2.2 ± 0.4</t>
+          <t>4.0 ± 0.8</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5209,37 +5209,37 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>41929.0 ± 166.2</t>
+          <t>70446.2 ± 200.7</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>24953.4 ± 124.0</t>
+          <t>41882.8 ± 137.4</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>129.4 ± 4.2</t>
+          <t>206.4 ± 5.3</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>16.0 ± 1.1</t>
+          <t>24.3 ± 1.5</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>74.0 ± 5.0</t>
+          <t>119.4 ± 4.9</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>37.0 ± 1.3</t>
+          <t>58.9 ± 2.4</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2.4 ± 0.4</t>
+          <t>3.9 ± 0.8</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5264,37 +5264,37 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>41591.6 ± 161.8</t>
+          <t>69827.1 ± 199.9</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>24581.4 ± 124.5</t>
+          <t>41176.2 ± 136.1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>126.6 ± 3.7</t>
+          <t>203.4 ± 5.2</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>15.2 ± 1.8</t>
+          <t>24.0 ± 1.6</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>73.2 ± 4.5</t>
+          <t>117.8 ± 4.7</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>36.0 ± 1.1</t>
+          <t>57.7 ± 2.6</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2.2 ± 0.5</t>
+          <t>3.9 ± 0.8</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5319,37 +5319,37 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>41204.2 ± 156.2</t>
+          <t>69177.9 ± 201.9</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>24148.0 ± 118.0</t>
+          <t>40484.4 ± 137.7</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>123.0 ± 4.1</t>
+          <t>201.4 ± 5.6</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>15.4 ± 1.9</t>
+          <t>24.2 ± 1.7</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>70.8 ± 4.5</t>
+          <t>116.2 ± 4.7</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>34.4 ± 0.9</t>
+          <t>57.5 ± 2.7</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2.4 ± 0.4</t>
+          <t>3.6 ± 0.7</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5374,37 +5374,37 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>40825.4 ± 158.7</t>
+          <t>68523.4 ± 205.7</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>23715.8 ± 120.5</t>
+          <t>39778.6 ± 137.0</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>120.8 ± 3.8</t>
+          <t>198.3 ± 5.4</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>15.0 ± 2.1</t>
+          <t>24.0 ± 1.7</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.6 ± 4.4</t>
+          <t>114.6 ± 4.7</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>33.8 ± 1.4</t>
+          <t>56.3 ± 2.5</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2.4 ± 0.2</t>
+          <t>3.5 ± 0.7</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5429,37 +5429,37 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>40443.8 ± 162.4</t>
+          <t>67877.4 ± 204.0</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>23300.8 ± 118.6</t>
+          <t>39064.3 ± 133.9</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>117.0 ± 3.5</t>
+          <t>194.3 ± 5.1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>14.0 ± 1.5</t>
+          <t>23.1 ± 1.7</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>68.0 ± 4.1</t>
+          <t>112.6 ± 4.4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>32.6 ± 1.3</t>
+          <t>55.2 ± 2.5</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2.4 ± 0.2</t>
+          <t>3.4 ± 0.7</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5484,37 +5484,37 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>40050.2 ± 164.5</t>
+          <t>67236.4 ± 196.9</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>22914.4 ± 117.7</t>
+          <t>38391.2 ± 124.7</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>116.0 ± 2.9</t>
+          <t>190.7 ± 4.7</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>13.6 ± 1.4</t>
+          <t>22.2 ± 1.7</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>68.8 ± 3.3</t>
+          <t>111.0 ± 4.2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>31.2 ± 1.0</t>
+          <t>54.0 ± 2.4</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2.4 ± 0.2</t>
+          <t>3.5 ± 0.7</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5539,37 +5539,37 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>39672.8 ± 175.5</t>
+          <t>66586.3 ± 195.9</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>22565.8 ± 116.5</t>
+          <t>37773.4 ± 120.2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>114.2 ± 3.3</t>
+          <t>187.8 ± 4.7</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>14.0 ± 1.4</t>
+          <t>21.3 ± 1.5</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>67.0 ± 3.4</t>
+          <t>109.1 ± 4.2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>31.0 ± 1.2</t>
+          <t>53.8 ± 2.4</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2.2 ± 0.2</t>
+          <t>3.6 ± 0.7</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5594,37 +5594,37 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>39300.4 ± 174.2</t>
+          <t>65946.0 ± 194.2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>22256.4 ± 119.3</t>
+          <t>37267.5 ± 117.0</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>112.8 ± 2.9</t>
+          <t>185.6 ± 4.6</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>14.0 ± 1.3</t>
+          <t>20.9 ± 1.6</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>67.0 ± 3.0</t>
+          <t>107.0 ± 4.0</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>29.6 ± 1.4</t>
+          <t>54.2 ± 2.5</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2.2 ± 0.2</t>
+          <t>3.5 ± 0.7</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5649,37 +5649,37 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>38915.6 ± 177.9</t>
+          <t>65309.4 ± 192.6</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>22004.6 ± 119.9</t>
+          <t>36847.9 ± 114.8</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>110.2 ± 2.4</t>
+          <t>183.7 ± 5.1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>13.4 ± 0.8</t>
+          <t>20.7 ± 1.6</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>65.6 ± 2.3</t>
+          <t>105.7 ± 4.3</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>29.0 ± 1.4</t>
+          <t>53.5 ± 2.6</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2.2 ± 0.2</t>
+          <t>3.8 ± 0.8</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5704,37 +5704,37 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>38546.4 ± 168.7</t>
+          <t>64699.8 ± 189.0</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>21741.4 ± 120.4</t>
+          <t>36426.7 ± 110.3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>108.2 ± 2.2</t>
+          <t>180.4 ± 5.4</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>13.2 ± 0.9</t>
+          <t>20.5 ± 1.7</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>64.0 ± 2.1</t>
+          <t>104.0 ± 4.2</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>28.8 ± 1.0</t>
+          <t>52.1 ± 2.7</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2.2 ± 0.2</t>
+          <t>3.8 ± 0.8</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5759,37 +5759,37 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>38176.0 ± 170.7</t>
+          <t>64089.0 ± 184.0</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>21502.0 ± 114.0</t>
+          <t>36005.6 ± 106.6</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>106.4 ± 1.8</t>
+          <t>177.8 ± 5.2</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>13.6 ± 1.3</t>
+          <t>19.8 ± 1.9</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.6 ± 2.2</t>
+          <t>102.5 ± 4.2</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>29.2 ± 0.9</t>
+          <t>51.7 ± 2.7</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2.0 ± 0.3</t>
+          <t>3.8 ± 0.8</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5814,37 +5814,37 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>37808.0 ± 157.0</t>
+          <t>63479.8 ± 184.4</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>21283.4 ± 101.6</t>
+          <t>35662.5 ± 105.6</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>106.8 ± 1.2</t>
+          <t>175.9 ± 4.7</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>13.8 ± 1.1</t>
+          <t>19.6 ± 1.8</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.6 ± 2.2</t>
+          <t>101.5 ± 4.0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>29.0 ± 1.2</t>
+          <t>51.1 ± 2.6</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2.4 ± 0.2</t>
+          <t>3.7 ± 0.9</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5869,37 +5869,37 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>37465.0 ± 166.8</t>
+          <t>62891.1 ± 182.9</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>21091.8 ± 104.9</t>
+          <t>35339.6 ± 103.0</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>105.6 ± 0.3</t>
+          <t>174.2 ± 4.8</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>13.8 ± 0.9</t>
+          <t>19.4 ± 1.7</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>60.6 ± 2.1</t>
+          <t>101.2 ± 3.9</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>28.8 ± 1.5</t>
+          <t>50.1 ± 2.5</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2.4 ± 0.2</t>
+          <t>3.5 ± 0.8</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5924,37 +5924,37 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>37127.8 ± 165.1</t>
+          <t>62293.5 ± 179.9</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>20990.6 ± 101.1</t>
+          <t>35135.9 ± 104.4</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>102.8 ± 0.9</t>
+          <t>173.7 ± 4.8</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>13.6 ± 0.8</t>
+          <t>19.6 ± 1.7</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>58.8 ± 2.2</t>
+          <t>101.1 ± 3.8</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>28.2 ± 1.7</t>
+          <t>49.4 ± 2.4</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2.2 ± 0.2</t>
+          <t>3.6 ± 0.8</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5979,37 +5979,37 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>36783.0 ± 170.8</t>
+          <t>61688.1 ± 177.1</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>20923.0 ± 102.4</t>
+          <t>35001.3 ± 107.3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>103.2 ± 0.8</t>
+          <t>173.6 ± 5.3</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>13.8 ± 0.7</t>
+          <t>19.9 ± 1.8</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>59.2 ± 2.2</t>
+          <t>101.3 ± 3.8</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>28.0 ± 1.8</t>
+          <t>48.9 ± 2.7</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2.2 ± 0.2</t>
+          <t>3.5 ± 0.8</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6034,37 +6034,37 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>36436.6 ± 171.4</t>
+          <t>61099.1 ± 176.6</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>20858.4 ± 105.6</t>
+          <t>34910.0 ± 105.6</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>103.8 ± 1.1</t>
+          <t>173.8 ± 5.6</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>13.4 ± 0.7</t>
+          <t>20.1 ± 1.9</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>60.2 ± 2.3</t>
+          <t>101.7 ± 3.9</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>28.2 ± 2.2</t>
+          <t>48.5 ± 2.7</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2.0 ± 0.4</t>
+          <t>3.6 ± 0.8</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6089,37 +6089,37 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>36103.8 ± 163.8</t>
+          <t>60494.2 ± 178.0</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>20804.4 ± 108.1</t>
+          <t>34798.3 ± 110.5</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>104.2 ± 1.5</t>
+          <t>174.9 ± 5.7</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>13.2 ± 0.7</t>
+          <t>19.8 ± 1.8</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>60.0 ± 2.4</t>
+          <t>102.5 ± 3.8</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>28.8 ± 2.0</t>
+          <t>49.1 ± 2.8</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2.2 ± 0.5</t>
+          <t>3.6 ± 0.8</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6144,37 +6144,37 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>35740.2 ± 171.4</t>
+          <t>59896.2 ± 180.5</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>20692.8 ± 108.8</t>
+          <t>34627.7 ± 114.7</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>104.0 ± 1.7</t>
+          <t>173.9 ± 5.8</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>13.2 ± 0.9</t>
+          <t>19.8 ± 1.9</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>59.6 ± 2.6</t>
+          <t>101.9 ± 3.9</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>29.0 ± 2.1</t>
+          <t>48.8 ± 2.7</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2.2 ± 0.5</t>
+          <t>3.5 ± 0.8</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6199,37 +6199,37 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>35388.4 ± 164.7</t>
+          <t>59282.2 ± 183.6</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>20551.6 ± 101.9</t>
+          <t>34393.3 ± 114.9</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>103.2 ± 1.0</t>
+          <t>174.1 ± 6.0</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>13.4 ± 0.9</t>
+          <t>19.7 ± 1.7</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>58.6 ± 2.2</t>
+          <t>101.5 ± 4.0</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>29.0 ± 1.7</t>
+          <t>49.3 ± 2.4</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2.2 ± 0.5</t>
+          <t>3.6 ± 0.8</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6254,37 +6254,37 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>35019.8 ± 163.2</t>
+          <t>58673.3 ± 188.6</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>20444.8 ± 104.5</t>
+          <t>34210.1 ± 121.6</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>101.4 ± 0.9</t>
+          <t>174.2 ± 5.5</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>12.6 ± 0.8</t>
+          <t>19.4 ± 1.8</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>58.4 ± 2.3</t>
+          <t>102.1 ± 3.7</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>28.4 ± 1.7</t>
+          <t>49.0 ± 2.3</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2.0 ± 0.4</t>
+          <t>3.6 ± 0.8</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6309,37 +6309,37 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>34669.4 ± 170.5</t>
+          <t>58063.8 ± 192.0</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>20328.2 ± 105.3</t>
+          <t>34000.9 ± 124.4</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>101.0 ± 0.5</t>
+          <t>171.9 ± 5.9</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>13.2 ± 0.8</t>
+          <t>19.1 ± 1.7</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>57.6 ± 2.4</t>
+          <t>101.2 ± 3.8</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>28.4 ± 1.7</t>
+          <t>48.1 ± 2.3</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1.8 ± 0.3</t>
+          <t>3.6 ± 0.8</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6364,37 +6364,37 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>34293.4 ± 173.7</t>
+          <t>57442.2 ± 192.6</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>20157.8 ± 107.3</t>
+          <t>33722.9 ± 130.4</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>101.0 ± 0.4</t>
+          <t>170.7 ± 6.0</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>13.4 ± 0.6</t>
+          <t>19.0 ± 1.6</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>56.8 ± 2.1</t>
+          <t>100.2 ± 4.3</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>29.0 ± 1.8</t>
+          <t>47.9 ± 2.2</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1.8 ± 0.3</t>
+          <t>3.5 ± 0.8</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6419,37 +6419,37 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>33898.0 ± 173.4</t>
+          <t>56825.2 ± 192.2</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>19989.4 ± 109.1</t>
+          <t>33443.2 ± 128.7</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>101.8 ± 1.0</t>
+          <t>168.7 ± 6.0</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>13.8 ± 0.7</t>
+          <t>18.9 ± 1.8</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>57.2 ± 1.6</t>
+          <t>98.7 ± 4.1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>29.0 ± 2.0</t>
+          <t>47.7 ± 2.2</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>1.8 ± 0.3</t>
+          <t>3.5 ± 0.9</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6474,37 +6474,37 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>33529.2 ± 175.0</t>
+          <t>56188.1 ± 189.8</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>19775.6 ± 106.0</t>
+          <t>33092.9 ± 132.9</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>100.0 ± 0.8</t>
+          <t>167.3 ± 6.1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>13.6 ± 0.7</t>
+          <t>18.4 ± 1.7</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>55.8 ± 1.7</t>
+          <t>98.0 ± 4.3</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>28.8 ± 2.0</t>
+          <t>47.5 ± 2.1</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1.8 ± 0.3</t>
+          <t>3.5 ± 0.8</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6529,37 +6529,37 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>33134.0 ± 161.2</t>
+          <t>55543.2 ± 188.6</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>19558.4 ± 96.0</t>
+          <t>32737.7 ± 130.8</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>96.2 ± 0.9</t>
+          <t>165.3 ± 6.3</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>13.6 ± 0.6</t>
+          <t>18.3 ± 1.6</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>53.2 ± 2.1</t>
+          <t>97.2 ± 4.3</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>27.6 ± 2.0</t>
+          <t>46.4 ± 1.9</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>1.8 ± 0.3</t>
+          <t>3.5 ± 0.8</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6584,37 +6584,37 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>32763.0 ± 155.7</t>
+          <t>54906.6 ± 190.7</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>19327.6 ± 99.2</t>
+          <t>32376.8 ± 128.8</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>96.0 ± 1.3</t>
+          <t>162.7 ± 6.3</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>13.6 ± 0.7</t>
+          <t>17.9 ± 1.7</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>53.8 ± 1.8</t>
+          <t>96.2 ± 4.6</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>26.8 ± 2.0</t>
+          <t>45.2 ± 2.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>1.8 ± 0.3</t>
+          <t>3.4 ± 0.8</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -6639,37 +6639,37 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>32384.8 ± 149.6</t>
+          <t>54283.5 ± 185.4</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>19079.8 ± 91.8</t>
+          <t>31972.7 ± 130.5</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>95.2 ± 0.7</t>
+          <t>160.8 ± 6.4</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>14.2 ± 0.6</t>
+          <t>17.8 ± 1.7</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>53.6 ± 2.0</t>
+          <t>94.7 ± 4.8</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>25.8 ± 1.8</t>
+          <t>44.9 ± 1.8</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1.6 ± 0.3</t>
+          <t>3.4 ± 0.8</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6694,37 +6694,37 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>32020.8 ± 153.6</t>
+          <t>53659.0 ± 184.0</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>18841.6 ± 95.2</t>
+          <t>31559.0 ± 130.6</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>93.8 ± 1.2</t>
+          <t>158.6 ± 6.4</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>13.2 ± 0.8</t>
+          <t>17.6 ± 1.7</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>53.2 ± 1.6</t>
+          <t>93.5 ± 4.6</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>25.6 ± 2.0</t>
+          <t>44.2 ± 1.9</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1.8 ± 0.4</t>
+          <t>3.3 ± 0.7</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -6749,37 +6749,37 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>31654.0 ± 154.2</t>
+          <t>53048.2 ± 184.0</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>18570.8 ± 93.3</t>
+          <t>31102.5 ± 127.7</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>93.0 ± 0.8</t>
+          <t>156.1 ± 6.6</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>13.0 ± 0.7</t>
+          <t>17.2 ± 1.7</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>53.6 ± 1.9</t>
+          <t>91.6 ± 4.7</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>24.4 ± 2.2</t>
+          <t>44.1 ± 2.0</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2.0 ± 0.5</t>
+          <t>3.1 ± 0.7</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -6804,37 +6804,37 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>31297.2 ± 142.7</t>
+          <t>52426.2 ± 185.3</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>18345.8 ± 91.8</t>
+          <t>30679.7 ± 130.7</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>91.6 ± 1.1</t>
+          <t>154.4 ± 6.4</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>12.6 ± 0.7</t>
+          <t>17.2 ± 1.6</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>53.0 ± 1.8</t>
+          <t>90.2 ± 4.8</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>24.0 ± 2.1</t>
+          <t>43.8 ± 2.1</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2.0 ± 0.5</t>
+          <t>3.1 ± 0.7</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -6859,37 +6859,37 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>30924.2 ± 137.1</t>
+          <t>51834.2 ± 183.7</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>18090.0 ± 84.9</t>
+          <t>30293.0 ± 134.2</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>89.2 ± 1.2</t>
+          <t>152.9 ± 6.4</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>12.4 ± 0.5</t>
+          <t>16.9 ± 1.5</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>50.8 ± 1.9</t>
+          <t>89.6 ± 4.9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>23.8 ± 2.1</t>
+          <t>43.4 ± 2.2</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2.2 ± 0.6</t>
+          <t>3.1 ± 0.6</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6914,37 +6914,37 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>30580.4 ± 130.1</t>
+          <t>51230.7 ± 184.1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>17831.0 ± 72.0</t>
+          <t>29895.8 ± 135.6</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>87.6 ± 1.2</t>
+          <t>150.8 ± 6.2</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>12.0 ± 0.6</t>
+          <t>17.1 ± 1.4</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>50.2 ± 2.2</t>
+          <t>88.1 ± 4.7</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>23.2 ± 2.0</t>
+          <t>42.5 ± 2.3</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2.2 ± 0.6</t>
+          <t>3.1 ± 0.6</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -6969,37 +6969,37 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>30220.8 ± 131.1</t>
+          <t>50634.9 ± 184.8</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>17587.8 ± 65.2</t>
+          <t>29514.4 ± 132.6</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>85.8 ± 1.7</t>
+          <t>150.2 ± 6.0</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>11.8 ± 0.8</t>
+          <t>17.1 ± 1.5</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>49.0 ± 2.3</t>
+          <t>87.5 ± 4.8</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>22.8 ± 2.1</t>
+          <t>42.5 ± 2.2</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2.2 ± 0.6</t>
+          <t>3.1 ± 0.6</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7024,37 +7024,37 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>29857.2 ± 123.7</t>
+          <t>50037.1 ± 179.3</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>17374.4 ± 68.5</t>
+          <t>29148.6 ± 128.7</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>86.0 ± 2.2</t>
+          <t>147.2 ± 6.3</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>11.8 ± 0.9</t>
+          <t>16.4 ± 1.7</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>49.6 ± 2.7</t>
+          <t>86.3 ± 4.9</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>22.2 ± 2.0</t>
+          <t>41.5 ± 2.3</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2.4 ± 0.5</t>
+          <t>2.9 ± 0.6</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7079,37 +7079,37 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>29500.2 ± 124.4</t>
+          <t>49422.1 ± 177.4</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>17130.4 ± 57.2</t>
+          <t>28756.4 ± 123.3</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>84.8 ± 2.4</t>
+          <t>144.7 ± 5.7</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>11.8 ± 1.2</t>
+          <t>16.3 ± 1.7</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>48.6 ± 2.9</t>
+          <t>85.0 ± 4.7</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>22.0 ± 2.2</t>
+          <t>40.6 ± 2.2</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2.4 ± 0.5</t>
+          <t>2.8 ± 0.6</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7134,37 +7134,37 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>29149.8 ± 126.6</t>
+          <t>48821.2 ± 180.7</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>16923.0 ± 57.4</t>
+          <t>28387.7 ± 122.8</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>84.0 ± 2.5</t>
+          <t>141.9 ± 5.9</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>11.2 ± 1.2</t>
+          <t>16.1 ± 1.7</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>48.4 ± 3.0</t>
+          <t>83.0 ± 4.5</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>22.0 ± 2.7</t>
+          <t>40.0 ± 2.2</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2.4 ± 0.5</t>
+          <t>2.8 ± 0.6</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7189,37 +7189,37 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>28811.8 ± 113.4</t>
+          <t>48222.7 ± 179.5</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>16713.8 ± 61.0</t>
+          <t>28044.2 ± 121.0</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>84.4 ± 2.4</t>
+          <t>139.8 ± 5.8</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>11.0 ± 1.3</t>
+          <t>15.8 ± 1.6</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>48.4 ± 3.1</t>
+          <t>82.3 ± 4.5</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>22.4 ± 2.7</t>
+          <t>39.0 ± 2.2</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2.6 ± 0.5</t>
+          <t>2.6 ± 0.6</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7244,37 +7244,37 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>28465.4 ± 111.3</t>
+          <t>47644.9 ± 179.1</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>16493.6 ± 61.2</t>
+          <t>27639.6 ± 119.7</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>83.4 ± 3.1</t>
+          <t>137.7 ± 5.6</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>10.8 ± 1.4</t>
+          <t>15.6 ± 1.7</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>47.2 ± 2.8</t>
+          <t>81.3 ± 4.5</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>22.6 ± 2.6</t>
+          <t>38.1 ± 1.8</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2.8 ± 0.5</t>
+          <t>2.5 ± 0.7</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -7299,37 +7299,37 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>28118.8 ± 108.4</t>
+          <t>47071.8 ± 182.7</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>16299.4 ± 67.0</t>
+          <t>27316.6 ± 120.6</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>81.4 ± 3.2</t>
+          <t>135.4 ± 5.1</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>11.0 ± 1.3</t>
+          <t>15.4 ± 1.5</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>45.6 ± 3.2</t>
+          <t>79.8 ± 4.2</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>22.0 ± 2.6</t>
+          <t>37.5 ± 1.8</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2.8 ± 0.5</t>
+          <t>2.5 ± 0.8</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7354,37 +7354,37 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>27775.6 ± 111.2</t>
+          <t>46502.7 ± 180.5</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>16135.2 ± 70.5</t>
+          <t>26994.2 ± 120.2</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>80.4 ± 2.0</t>
+          <t>133.9 ± 4.9</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>10.6 ± 1.5</t>
+          <t>15.3 ± 1.6</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>44.8 ± 3.4</t>
+          <t>78.6 ± 4.4</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>22.8 ± 2.6</t>
+          <t>37.4 ± 1.8</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2.2 ± 0.6</t>
+          <t>2.6 ± 0.7</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7409,37 +7409,37 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>27454.4 ± 105.3</t>
+          <t>45940.9 ± 178.1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>15976.2 ± 68.9</t>
+          <t>26709.8 ± 117.1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>78.6 ± 2.7</t>
+          <t>132.2 ± 5.2</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>10.2 ± 1.5</t>
+          <t>15.2 ± 1.4</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>43.6 ± 3.5</t>
+          <t>78.4 ± 4.4</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>22.6 ± 2.4</t>
+          <t>36.0 ± 1.8</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2.2 ± 0.6</t>
+          <t>2.6 ± 0.7</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7464,37 +7464,37 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>27132.2 ± 103.0</t>
+          <t>45392.8 ± 175.5</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>15816.6 ± 67.8</t>
+          <t>26432.2 ± 114.5</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>77.6 ± 4.0</t>
+          <t>131.1 ± 5.0</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>10.0 ± 1.5</t>
+          <t>15.1 ± 1.4</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>43.4 ± 3.5</t>
+          <t>78.2 ± 4.4</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>22.0 ± 2.6</t>
+          <t>35.5 ± 1.8</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2.2 ± 0.6</t>
+          <t>2.4 ± 0.7</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -7519,37 +7519,37 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>26821.4 ± 104.1</t>
+          <t>44875.3 ± 174.3</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>15650.6 ± 70.7</t>
+          <t>26178.6 ± 115.5</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>75.4 ± 4.1</t>
+          <t>129.3 ± 5.1</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>10.0 ± 1.3</t>
+          <t>14.8 ± 1.4</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>42.0 ± 3.3</t>
+          <t>77.3 ± 4.5</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>21.6 ± 2.6</t>
+          <t>35.0 ± 1.8</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>1.8 ± 0.5</t>
+          <t>2.3 ± 0.7</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -7574,37 +7574,37 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>26515.6 ± 101.9</t>
+          <t>44379.9 ± 176.4</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>15499.2 ± 68.0</t>
+          <t>25913.5 ± 117.1</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>74.2 ± 3.4</t>
+          <t>129.6 ± 4.8</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>10.2 ± 1.0</t>
+          <t>14.9 ± 1.4</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>41.0 ± 2.9</t>
+          <t>77.5 ± 4.2</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>21.2 ± 2.5</t>
+          <t>34.9 ± 1.8</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>1.8 ± 0.5</t>
+          <t>2.3 ± 0.7</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7629,37 +7629,37 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>26265.4 ± 103.8</t>
+          <t>43926.2 ± 175.4</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>15361.2 ± 72.8</t>
+          <t>25671.6 ± 112.0</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>73.6 ± 3.1</t>
+          <t>129.1 ± 4.8</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>10.0 ± 1.0</t>
+          <t>14.8 ± 1.4</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>41.0 ± 2.3</t>
+          <t>76.8 ± 3.8</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20.6 ± 2.5</t>
+          <t>35.1 ± 1.9</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2.0 ± 0.4</t>
+          <t>2.2 ± 0.7</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7684,37 +7684,37 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>26000.0 ± 100.5</t>
+          <t>43462.6 ± 171.3</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>15218.2 ± 74.2</t>
+          <t>25426.8 ± 107.0</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>72.6 ± 3.3</t>
+          <t>128.6 ± 4.7</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>10.2 ± 1.0</t>
+          <t>14.8 ± 1.2</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>40.6 ± 2.2</t>
+          <t>76.5 ± 4.0</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20.0 ± 2.5</t>
+          <t>35.1 ± 1.8</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>1.8 ± 0.4</t>
+          <t>2.1 ± 0.6</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -7739,37 +7739,37 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>25738.4 ± 101.0</t>
+          <t>43021.8 ± 168.1</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>15073.4 ± 80.0</t>
+          <t>25199.8 ± 108.1</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>72.6 ± 3.8</t>
+          <t>126.3 ± 4.9</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>10.6 ± 1.2</t>
+          <t>14.6 ± 1.2</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>40.6 ± 1.7</t>
+          <t>75.2 ± 4.0</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>19.6 ± 2.6</t>
+          <t>34.4 ± 1.7</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>1.8 ± 0.4</t>
+          <t>2.2 ± 0.6</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -7794,37 +7794,37 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>25478.8 ± 102.4</t>
+          <t>42595.8 ± 164.9</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>14928.2 ± 82.9</t>
+          <t>24962.3 ± 112.9</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>74.4 ± 3.3</t>
+          <t>125.7 ± 5.0</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>10.6 ± 1.1</t>
+          <t>14.6 ± 1.3</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>41.2 ± 1.3</t>
+          <t>74.8 ± 4.0</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20.8 ± 2.5</t>
+          <t>34.1 ± 1.9</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>1.8 ± 0.4</t>
+          <t>2.1 ± 0.6</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7849,37 +7849,37 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>25216.8 ± 98.1</t>
+          <t>42175.6 ± 170.3</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>14779.2 ± 91.1</t>
+          <t>24725.2 ± 118.3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>74.4 ± 3.1</t>
+          <t>124.6 ± 4.8</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>10.8 ± 1.1</t>
+          <t>14.8 ± 1.3</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>41.2 ± 1.2</t>
+          <t>74.0 ± 3.7</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20.6 ± 2.4</t>
+          <t>33.8 ± 1.8</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>1.8 ± 0.4</t>
+          <t>1.9 ± 0.5</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -7904,37 +7904,37 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>25016.6 ± 95.3</t>
+          <t>41794.3 ± 173.2</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>14648.0 ± 86.4</t>
+          <t>24486.8 ± 115.2</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>73.6 ± 2.5</t>
+          <t>123.5 ± 4.6</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>11.0 ± 1.1</t>
+          <t>14.8 ± 1.2</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>40.8 ± 1.3</t>
+          <t>73.3 ± 3.8</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20.0 ± 2.0</t>
+          <t>33.4 ± 1.8</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>1.8 ± 0.4</t>
+          <t>2.0 ± 0.5</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -7959,32 +7959,32 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>24798.0 ± 89.9</t>
+          <t>41425.8 ± 170.7</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>14509.6 ± 88.3</t>
+          <t>24234.5 ± 114.5</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>73.4 ± 2.5</t>
+          <t>122.2 ± 4.2</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>10.4 ± 0.9</t>
+          <t>14.6 ± 1.2</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>41.4 ± 2.1</t>
+          <t>72.1 ± 3.4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>19.8 ± 2.0</t>
+          <t>33.8 ± 1.7</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8014,37 +8014,37 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>24578.0 ± 94.0</t>
+          <t>41081.8 ± 174.3</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>14351.4 ± 90.6</t>
+          <t>23996.7 ± 113.5</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>72.4 ± 2.7</t>
+          <t>122.0 ± 4.3</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>10.4 ± 0.9</t>
+          <t>14.5 ± 1.2</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>41.0 ± 1.9</t>
+          <t>72.3 ± 3.3</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>19.2 ± 2.1</t>
+          <t>33.4 ± 1.7</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>1.8 ± 0.2</t>
+          <t>1.8 ± 0.5</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8069,37 +8069,37 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>24370.4 ± 92.9</t>
+          <t>40727.2 ± 175.8</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>14211.0 ± 88.6</t>
+          <t>23754.7 ± 115.2</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>70.6 ± 2.0</t>
+          <t>120.6 ± 4.6</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>10.4 ± 0.7</t>
+          <t>14.3 ± 1.2</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>39.4 ± 1.9</t>
+          <t>71.5 ± 3.2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>19.0 ± 2.0</t>
+          <t>33.1 ± 1.9</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>1.8 ± 0.2</t>
+          <t>1.6 ± 0.4</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8124,37 +8124,37 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>24146.2 ± 93.0</t>
+          <t>40345.4 ± 176.0</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>14086.0 ± 90.1</t>
+          <t>23500.0 ± 118.2</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>70.4 ± 1.7</t>
+          <t>119.5 ± 4.5</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>9.8 ± 0.8</t>
+          <t>13.8 ± 1.2</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>39.8 ± 1.8</t>
+          <t>70.8 ± 3.1</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>19.0 ± 2.1</t>
+          <t>33.1 ± 2.1</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>1.8 ± 0.2</t>
+          <t>1.6 ± 0.5</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8179,37 +8179,37 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>23920.2 ± 92.7</t>
+          <t>39951.4 ± 179.4</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>13939.6 ± 87.8</t>
+          <t>23243.3 ± 121.9</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>70.6 ± 1.6</t>
+          <t>117.6 ± 4.5</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>9.4 ± 0.8</t>
+          <t>13.9 ± 1.2</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>40.4 ± 2.1</t>
+          <t>70.0 ± 3.3</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>19.2 ± 1.8</t>
+          <t>32.4 ± 2.0</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>1.6 ± 0.2</t>
+          <t>1.4 ± 0.5</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8234,37 +8234,37 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>23679.2 ± 95.5</t>
+          <t>39574.2 ± 180.1</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>13782.8 ± 89.6</t>
+          <t>22984.0 ± 118.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>71.0 ± 1.7</t>
+          <t>115.8 ± 4.3</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>9.2 ± 1.0</t>
+          <t>13.7 ± 1.3</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>40.8 ± 1.7</t>
+          <t>68.7 ± 3.0</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>19.4 ± 1.9</t>
+          <t>32.0 ± 1.8</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>1.6 ± 0.2</t>
+          <t>1.4 ± 0.5</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8289,37 +8289,37 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>23471.2 ± 100.8</t>
+          <t>39183.2 ± 181.1</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>13630.0 ± 91.7</t>
+          <t>22725.1 ± 122.4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>69.6 ± 1.5</t>
+          <t>114.7 ± 4.6</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>8.8 ± 1.1</t>
+          <t>13.2 ± 1.2</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>40.0 ± 2.3</t>
+          <t>68.3 ± 3.1</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>19.0 ± 1.8</t>
+          <t>31.6 ± 1.6</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>1.8 ± 0.3</t>
+          <t>1.6 ± 0.5</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8344,37 +8344,37 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>23211.4 ± 96.6</t>
+          <t>38769.1 ± 182.3</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>13469.4 ± 78.8</t>
+          <t>22454.5 ± 125.5</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>70.4 ± 1.5</t>
+          <t>113.2 ± 4.6</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>9.0 ± 0.9</t>
+          <t>13.2 ± 1.3</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>40.4 ± 2.3</t>
+          <t>67.8 ± 3.0</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>19.4 ± 1.7</t>
+          <t>30.6 ± 1.7</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>1.6 ± 0.3</t>
+          <t>1.6 ± 0.5</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8399,37 +8399,37 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>22967.2 ± 100.0</t>
+          <t>38364.0 ± 175.5</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>13308.0 ± 77.6</t>
+          <t>22200.3 ± 125.3</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>69.0 ± 1.8</t>
+          <t>112.9 ± 4.9</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>9.2 ± 0.8</t>
+          <t>12.9 ± 1.4</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>39.6 ± 2.2</t>
+          <t>68.3 ± 3.4</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>18.8 ± 1.1</t>
+          <t>30.0 ± 1.6</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>1.4 ± 0.3</t>
+          <t>1.7 ± 0.5</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8454,37 +8454,37 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>22714.4 ± 83.0</t>
+          <t>37941.6 ± 177.1</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>13169.0 ± 70.7</t>
+          <t>21934.6 ± 122.5</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>66.8 ± 2.2</t>
+          <t>111.5 ± 4.9</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>9.2 ± 0.8</t>
+          <t>12.8 ± 1.4</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>37.8 ± 2.1</t>
+          <t>67.4 ± 3.4</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>18.4 ± 1.3</t>
+          <t>29.8 ± 1.8</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>1.4 ± 0.3</t>
+          <t>1.6 ± 0.5</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -8509,37 +8509,37 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>22463.8 ± 82.6</t>
+          <t>37516.7 ± 177.9</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>13013.4 ± 76.7</t>
+          <t>21670.2 ± 125.8</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>65.8 ± 1.4</t>
+          <t>109.2 ± 4.4</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>9.0 ± 0.7</t>
+          <t>12.4 ± 1.3</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>37.6 ± 1.7</t>
+          <t>65.7 ± 3.1</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>17.8 ± 1.0</t>
+          <t>29.4 ± 1.8</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>1.4 ± 0.3</t>
+          <t>1.6 ± 0.5</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -8564,37 +8564,37 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>22212.8 ± 83.7</t>
+          <t>37100.1 ± 177.6</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>12854.0 ± 68.1</t>
+          <t>21408.8 ± 121.6</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>64.6 ± 1.4</t>
+          <t>107.5 ± 4.4</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>9.0 ± 0.7</t>
+          <t>12.2 ± 1.2</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>37.2 ± 2.1</t>
+          <t>64.7 ± 3.2</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>17.0 ± 0.8</t>
+          <t>29.1 ± 1.7</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>1.4 ± 0.3</t>
+          <t>1.6 ± 0.5</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -8619,37 +8619,37 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>21959.2 ± 88.6</t>
+          <t>36661.4 ± 177.3</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>12716.6 ± 73.3</t>
+          <t>21149.0 ± 122.0</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>63.2 ± 1.5</t>
+          <t>105.6 ± 4.3</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>8.8 ± 0.9</t>
+          <t>11.7 ± 1.2</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>36.4 ± 2.1</t>
+          <t>63.8 ± 3.4</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>16.6 ± 0.7</t>
+          <t>28.6 ± 1.4</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>1.4 ± 0.3</t>
+          <t>1.6 ± 0.5</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -8674,37 +8674,37 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>21697.2 ± 86.9</t>
+          <t>36240.2 ± 174.4</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>12566.8 ± 80.3</t>
+          <t>20905.2 ± 119.8</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>63.2 ± 1.5</t>
+          <t>104.8 ± 4.4</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>8.8 ± 0.9</t>
+          <t>11.4 ± 1.3</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>36.4 ± 2.4</t>
+          <t>63.1 ± 3.4</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>16.6 ± 0.7</t>
+          <t>28.6 ± 1.5</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>1.4 ± 0.3</t>
+          <t>1.6 ± 0.5</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -8729,37 +8729,37 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>21437.8 ± 78.9</t>
+          <t>35795.3 ± 176.8</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>12424.2 ± 77.8</t>
+          <t>20667.1 ± 122.2</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>62.2 ± 1.6</t>
+          <t>103.8 ± 4.3</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>8.6 ± 1.1</t>
+          <t>11.4 ± 1.4</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>35.8 ± 2.7</t>
+          <t>62.0 ± 3.2</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>16.4 ± 0.8</t>
+          <t>28.6 ± 1.4</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>1.4 ± 0.3</t>
+          <t>1.6 ± 0.5</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -8784,37 +8784,37 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>21177.0 ± 80.5</t>
+          <t>35394.2 ± 178.1</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>12271.6 ± 74.4</t>
+          <t>20439.8 ± 123.2</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>61.2 ± 2.0</t>
+          <t>102.2 ± 4.3</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>8.4 ± 1.1</t>
+          <t>11.2 ± 1.4</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>35.6 ± 2.7</t>
+          <t>61.1 ± 3.2</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>15.8 ± 0.8</t>
+          <t>28.2 ± 1.6</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>1.4 ± 0.3</t>
+          <t>1.6 ± 0.5</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -8839,37 +8839,37 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>20924.4 ± 76.7</t>
+          <t>34987.2 ± 172.9</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>12140.4 ± 69.9</t>
+          <t>20209.6 ± 119.8</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>59.8 ± 2.2</t>
+          <t>100.8 ± 4.2</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>8.0 ± 1.0</t>
+          <t>11.2 ± 1.4</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>34.2 ± 2.6</t>
+          <t>60.4 ± 3.1</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>16.2 ± 0.9</t>
+          <t>27.7 ± 1.8</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>1.4 ± 0.3</t>
+          <t>1.6 ± 0.5</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -8894,37 +8894,37 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>20672.8 ± 83.4</t>
+          <t>34581.9 ± 175.5</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>12000.2 ± 67.2</t>
+          <t>19992.2 ± 118.4</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>58.4 ± 2.5</t>
+          <t>98.8 ± 4.2</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>7.4 ± 0.9</t>
+          <t>10.6 ± 1.5</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>33.4 ± 2.7</t>
+          <t>59.5 ± 3.3</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>16.4 ± 0.8</t>
+          <t>27.3 ± 1.9</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>1.2 ± 0.4</t>
+          <t>1.5 ± 0.5</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -8949,37 +8949,37 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>20453.6 ± 79.9</t>
+          <t>34200.4 ± 173.7</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>11866.6 ± 68.9</t>
+          <t>19774.7 ± 120.3</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>58.4 ± 2.6</t>
+          <t>97.5 ± 4.3</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>7.4 ± 0.9</t>
+          <t>10.7 ± 1.5</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>33.6 ± 2.7</t>
+          <t>58.6 ± 3.5</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>16.0 ± 1.1</t>
+          <t>26.7 ± 1.9</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>1.4 ± 0.3</t>
+          <t>1.4 ± 0.4</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9004,37 +9004,37 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>20228.0 ± 83.0</t>
+          <t>33814.3 ± 172.3</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>11734.0 ± 75.3</t>
+          <t>19548.8 ± 118.6</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>56.8 ± 2.6</t>
+          <t>96.5 ± 4.2</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>6.6 ± 0.5</t>
+          <t>10.7 ± 1.4</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>32.8 ± 2.5</t>
+          <t>58.0 ± 3.3</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>16.0 ± 1.1</t>
+          <t>26.4 ± 2.0</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>1.4 ± 0.3</t>
+          <t>1.4 ± 0.4</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -9059,37 +9059,37 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>19993.8 ± 80.4</t>
+          <t>33428.5 ± 172.3</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>11593.6 ± 72.0</t>
+          <t>19340.8 ± 119.2</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>55.8 ± 2.2</t>
+          <t>95.5 ± 3.9</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>6.6 ± 0.7</t>
+          <t>10.6 ± 1.4</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>32.4 ± 2.1</t>
+          <t>57.6 ± 3.4</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>15.4 ± 1.1</t>
+          <t>26.1 ± 1.8</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>1.4 ± 0.3</t>
+          <t>1.2 ± 0.4</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9114,37 +9114,37 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>19776.2 ± 84.7</t>
+          <t>33051.9 ± 167.2</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>11476.0 ± 74.0</t>
+          <t>19133.3 ± 116.6</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>54.8 ± 1.8</t>
+          <t>94.2 ± 4.0</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>6.2 ± 0.8</t>
+          <t>10.3 ± 1.4</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>32.4 ± 1.5</t>
+          <t>56.6 ± 3.6</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>14.8 ± 1.0</t>
+          <t>25.9 ± 1.7</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>1.4 ± 0.3</t>
+          <t>1.3 ± 0.4</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9169,37 +9169,37 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>19543.0 ± 93.2</t>
+          <t>32684.2 ± 168.4</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>11351.2 ± 73.2</t>
+          <t>18928.8 ± 119.7</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>54.4 ± 2.0</t>
+          <t>92.3 ± 3.5</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>6.2 ± 0.8</t>
+          <t>10.0 ± 1.5</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>32.0 ± 1.8</t>
+          <t>55.3 ± 3.2</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>14.8 ± 0.9</t>
+          <t>25.7 ± 1.6</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>1.4 ± 0.3</t>
+          <t>1.3 ± 0.4</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9224,37 +9224,37 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>19315.6 ± 86.7</t>
+          <t>32294.3 ± 169.4</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>11227.0 ± 75.9</t>
+          <t>18714.3 ± 119.0</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>54.0 ± 2.0</t>
+          <t>91.0 ± 3.7</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>5.8 ± 0.8</t>
+          <t>9.9 ± 1.5</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>31.6 ± 1.6</t>
+          <t>54.7 ± 3.4</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>15.2 ± 1.1</t>
+          <t>25.2 ± 1.5</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>1.4 ± 0.3</t>
+          <t>1.1 ± 0.4</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -9279,37 +9279,37 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>19088.2 ± 104.6</t>
+          <t>31939.6 ± 164.1</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>11115.4 ± 80.4</t>
+          <t>18514.6 ± 117.2</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>54.0 ± 1.8</t>
+          <t>90.0 ± 3.8</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>6.0 ± 0.8</t>
+          <t>10.1 ± 1.5</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>31.4 ± 1.6</t>
+          <t>53.5 ± 3.6</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>15.2 ± 0.9</t>
+          <t>25.2 ± 1.4</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>1.4 ± 0.3</t>
+          <t>1.1 ± 0.4</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -9334,37 +9334,37 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>18891.8 ± 108.9</t>
+          <t>31588.1 ± 160.8</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>10994.0 ± 88.4</t>
+          <t>18322.0 ± 114.4</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>53.0 ± 1.5</t>
+          <t>88.7 ± 3.9</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>5.6 ± 0.8</t>
+          <t>10.1 ± 1.5</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>31.6 ± 1.1</t>
+          <t>52.6 ± 3.6</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>14.6 ± 0.9</t>
+          <t>24.8 ± 1.5</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>1.2 ± 0.4</t>
+          <t>1.1 ± 0.4</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -9389,37 +9389,37 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>18697.4 ± 109.6</t>
+          <t>31259.4 ± 163.3</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>10892.0 ± 87.8</t>
+          <t>18121.0 ± 116.9</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>52.4 ± 1.4</t>
+          <t>87.8 ± 4.0</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>5.8 ± 0.7</t>
+          <t>10.0 ± 1.5</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>30.8 ± 1.1</t>
+          <t>52.0 ± 3.7</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>14.6 ± 0.9</t>
+          <t>24.6 ± 1.6</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>1.2 ± 0.4</t>
+          <t>1.1 ± 0.4</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -9444,37 +9444,37 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>18500.6 ± 112.0</t>
+          <t>30922.6 ± 160.9</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>10764.6 ± 89.2</t>
+          <t>17926.0 ± 116.4</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>52.6 ± 0.9</t>
+          <t>86.9 ± 3.6</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>5.8 ± 0.7</t>
+          <t>9.8 ± 1.5</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>30.4 ± 0.7</t>
+          <t>51.4 ± 3.4</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>15.2 ± 1.2</t>
+          <t>24.6 ± 1.3</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>1.2 ± 0.4</t>
+          <t>1.1 ± 0.4</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -9499,37 +9499,37 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>18322.4 ± 122.1</t>
+          <t>30590.9 ± 159.2</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>10655.0 ± 95.9</t>
+          <t>17726.1 ± 114.6</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>51.4 ± 0.9</t>
+          <t>86.2 ± 3.8</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>5.6 ± 0.8</t>
+          <t>9.8 ± 1.4</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>29.6 ± 0.4</t>
+          <t>50.8 ± 3.4</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>14.8 ± 1.3</t>
+          <t>24.4 ± 1.5</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>1.4 ± 0.4</t>
+          <t>1.2 ± 0.4</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -9554,37 +9554,37 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>18137.8 ± 126.5</t>
+          <t>30267.6 ± 159.8</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>10541.6 ± 95.6</t>
+          <t>17534.2 ± 114.7</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>51.0 ± 1.4</t>
+          <t>85.2 ± 3.8</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>6.0 ± 0.7</t>
+          <t>9.6 ± 1.3</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>29.6 ± 0.7</t>
+          <t>50.0 ± 3.4</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>14.4 ± 1.5</t>
+          <t>24.4 ± 1.4</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>1.2 ± 0.4</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -9609,37 +9609,37 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>17947.6 ± 124.2</t>
+          <t>29952.3 ± 164.5</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>10432.4 ± 98.6</t>
+          <t>17341.0 ± 113.1</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>50.2 ± 1.5</t>
+          <t>84.2 ± 3.8</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>5.6 ± 0.7</t>
+          <t>9.5 ± 1.3</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>29.4 ± 0.7</t>
+          <t>49.2 ± 3.4</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>14.2 ± 1.6</t>
+          <t>24.1 ± 1.5</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>1.3 ± 0.4</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -9664,37 +9664,37 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>17772.6 ± 120.2</t>
+          <t>29636.5 ± 162.4</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>10333.6 ± 93.9</t>
+          <t>17148.0 ± 112.7</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>48.8 ± 1.5</t>
+          <t>83.2 ± 3.6</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>5.2 ± 0.5</t>
+          <t>9.6 ± 1.3</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>28.4 ± 0.9</t>
+          <t>48.5 ± 3.3</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>14.4 ± 1.4</t>
+          <t>23.8 ± 1.5</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>0.8 ± 0.3</t>
+          <t>1.4 ± 0.4</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -9719,37 +9719,37 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>17587.8 ± 121.3</t>
+          <t>29323.0 ± 165.7</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>10214.0 ± 90.0</t>
+          <t>16962.7 ± 117.7</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>48.4 ± 1.3</t>
+          <t>81.7 ± 3.5</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>4.8 ± 0.6</t>
+          <t>9.5 ± 1.3</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>28.2 ± 0.9</t>
+          <t>47.0 ± 3.3</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>14.8 ± 1.6</t>
+          <t>23.8 ± 1.6</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>0.6 ± 0.3</t>
+          <t>1.3 ± 0.4</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -9774,37 +9774,37 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>17400.4 ± 124.6</t>
+          <t>29016.6 ± 166.3</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>10099.2 ± 90.5</t>
+          <t>16782.4 ± 120.2</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>48.2 ± 1.5</t>
+          <t>81.0 ± 3.4</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>4.8 ± 0.6</t>
+          <t>9.6 ± 1.3</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>28.4 ± 0.8</t>
+          <t>46.8 ± 3.4</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>14.4 ± 1.7</t>
+          <t>23.4 ± 1.6</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>0.6 ± 0.3</t>
+          <t>1.2 ± 0.4</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -9829,37 +9829,37 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>17221.6 ± 126.6</t>
+          <t>28710.7 ± 166.0</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>9990.0 ± 90.3</t>
+          <t>16603.5 ± 121.7</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>47.6 ± 1.6</t>
+          <t>79.9 ± 3.3</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>5.0 ± 0.7</t>
+          <t>9.2 ± 1.3</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>28.8 ± 1.1</t>
+          <t>46.6 ± 3.4</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>13.0 ± 1.4</t>
+          <t>22.9 ± 1.5</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>0.8 ± 0.5</t>
+          <t>1.1 ± 0.4</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -9884,37 +9884,37 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>17032.0 ± 123.0</t>
+          <t>28399.2 ± 163.8</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>9875.2 ± 88.5</t>
+          <t>16417.9 ± 121.2</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>47.4 ± 1.6</t>
+          <t>79.4 ± 3.4</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>5.0 ± 0.6</t>
+          <t>9.1 ± 1.2</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>28.8 ± 1.3</t>
+          <t>46.1 ± 3.5</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>12.8 ± 1.4</t>
+          <t>23.0 ± 1.5</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>0.8 ± 0.5</t>
+          <t>1.2 ± 0.4</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -9939,37 +9939,37 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>16856.8 ± 118.3</t>
+          <t>28097.3 ± 161.4</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>9770.4 ± 85.1</t>
+          <t>16241.1 ± 122.8</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>47.2 ± 2.0</t>
+          <t>78.1 ± 3.4</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>4.6 ± 0.6</t>
+          <t>8.5 ± 1.2</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>29.2 ± 1.3</t>
+          <t>45.8 ± 3.5</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>12.8 ± 1.4</t>
+          <t>22.6 ± 1.6</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>0.6 ± 0.5</t>
+          <t>1.2 ± 0.4</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -9994,37 +9994,37 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>16668.8 ± 124.7</t>
+          <t>27793.3 ± 164.7</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>9654.0 ± 88.2</t>
+          <t>16054.0 ± 123.2</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>47.0 ± 2.0</t>
+          <t>78.0 ± 3.6</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>4.4 ± 0.4</t>
+          <t>8.7 ± 1.2</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>29.2 ± 1.1</t>
+          <t>45.6 ± 3.6</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>12.8 ± 1.6</t>
+          <t>22.5 ± 1.6</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>0.6 ± 0.5</t>
+          <t>1.2 ± 0.4</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10049,37 +10049,37 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>16500.0 ± 131.1</t>
+          <t>27488.8 ± 166.3</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>9552.8 ± 91.3</t>
+          <t>15871.1 ± 121.3</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>45.4 ± 1.9</t>
+          <t>76.8 ± 3.6</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>4.0 ± 0.4</t>
+          <t>8.4 ± 1.2</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>28.8 ± 1.5</t>
+          <t>45.4 ± 3.4</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>12.0 ± 1.5</t>
+          <t>21.8 ± 1.6</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>0.6 ± 0.5</t>
+          <t>1.2 ± 0.4</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10104,37 +10104,37 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>16348.8 ± 131.0</t>
+          <t>27187.2 ± 169.4</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>9450.4 ± 88.6</t>
+          <t>15698.4 ± 122.5</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>44.2 ± 1.7</t>
+          <t>76.4 ± 3.6</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>4.0 ± 0.6</t>
+          <t>8.6 ± 1.2</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>27.6 ± 1.3</t>
+          <t>45.5 ± 3.5</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>12.2 ± 1.4</t>
+          <t>21.1 ± 1.6</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>0.4 ± 0.3</t>
+          <t>1.2 ± 0.4</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
